--- a/Selenium-Cucumber-BDD-POM-Framework/src/main/java/TestData/TestData.xlsx
+++ b/Selenium-Cucumber-BDD-POM-Framework/src/main/java/TestData/TestData.xlsx
@@ -3,14 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC758D9E-54BD-4DF5-95FC-CD295075CC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{73B1D442-7B70-46A9-8ACC-09536ED4F626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{789A8E90-410F-4C5F-A481-90ACB70F6E1C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{789A8E90-410F-4C5F-A481-90ACB70F6E1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +13,8 @@
     <sheet name="Testdata" sheetId="2" r:id="rId3"/>
     <sheet name="AccountID" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:O18"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="92">
   <si>
     <t>URL</t>
   </si>
@@ -280,6 +276,30 @@
   </si>
   <si>
     <t>54064</t>
+  </si>
+  <si>
+    <t>182178</t>
+  </si>
+  <si>
+    <t>64781</t>
+  </si>
+  <si>
+    <t>24185</t>
+  </si>
+  <si>
+    <t>182179</t>
+  </si>
+  <si>
+    <t>74734</t>
+  </si>
+  <si>
+    <t>77800</t>
+  </si>
+  <si>
+    <t>182185</t>
+  </si>
+  <si>
+    <t>5098</t>
   </si>
 </sst>
 </file>
@@ -316,11 +336,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -659,7 +680,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCFB0E3D-6B0C-4106-B64C-A25DAAB9D121}">
-  <dimension ref="A1:A46"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -857,39 +878,67 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s" s="0">
         <v>74</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s" s="0">
         <v>75</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s" s="0">
         <v>76</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s" s="0">
         <v>78</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s" s="0">
         <v>79</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s" s="0">
         <v>82</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s" s="0">
         <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s" s="0">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC5F77C-9CA2-407A-AAAD-0F97D6AEB135}">
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="11.0"/>
@@ -1121,19 +1170,34 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s" s="0">
         <v>77</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s" s="0">
         <v>80</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s" s="0">
         <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s" s="0">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s" s="0">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Selenium-Cucumber-BDD-POM-Framework/src/main/java/TestData/TestData.xlsx
+++ b/Selenium-Cucumber-BDD-POM-Framework/src/main/java/TestData/TestData.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="95">
   <si>
     <t>URL</t>
   </si>
@@ -300,6 +300,15 @@
   </si>
   <si>
     <t>5098</t>
+  </si>
+  <si>
+    <t>182193</t>
+  </si>
+  <si>
+    <t>16901</t>
+  </si>
+  <si>
+    <t>182194</t>
   </si>
 </sst>
 </file>
@@ -680,7 +689,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCFB0E3D-6B0C-4106-B64C-A25DAAB9D121}">
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -939,6 +948,11 @@
     <row r="52">
       <c r="A52" t="s" s="0">
         <v>91</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1044,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC5F77C-9CA2-407A-AAAD-0F97D6AEB135}">
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="11.0"/>
@@ -1200,6 +1214,16 @@
         <v>90</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
